--- a/vlearn-app/public/quiz_excel/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_03_19_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_03_19_Cau.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -689,7 +689,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Collector, Metric route.</t>
+          <t>Để loại bỏ tình trạng duplicate dữ liệu trace khi gửi trực tiếp và qua collector, kiến trúc chuẩn là định tuyến toàn bộ telemetry qua một OpenTelemetry Collector duy nhất và cấu hình fan-out rõ ràng tại đó.</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -795,7 +795,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Request counter, Latency observation.</t>
+          <t>Ghi nhận chỉ số đo lường chính xác: Tăng bộ đếm request ngay khi tiếp nhận (ingress), đo thời gian xử lý trong khối `finally`, và chỉ gắn nhãn thành công/thất bại tại sự kiện kết thúc cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50000000000000</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -843,7 +843,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số giá trị độc lập của từng label.</t>
+          <t>Upper bound số time series: Tích số các giá trị cardinality của từng metric label = 1.000.000 (user_id) * 10.000.000 (request_id) * 5 (model) = 5 * 10^13 = 50.000.000.000.000 series.</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -939,7 +939,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Overview, Engineering detail.</t>
+          <t>Thiết kế bảng điều khiển trực quan hiệu quả theo nguyên lý phân cấp nhận thức: Bắt đầu từ màn hình tổng quan mức cao (Overview) → xem chi tiết kỹ thuật (Detail) → cho phép đi sâu vào từng vết sự cố (Drill-down).</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60</v>
@@ -987,7 +987,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Named panel profile, Traffic.</t>
+          <t>Bảng điều khiển hiện tại vi phạm nghiêm trọng yêu cầu đặc tả vì thiếu cả bốn liên kết chỉ số trọng yếu: TTFT P95, chi phí tác vụ P95, tỷ lệ lỗi công cụ và độ tin cậy nội dung (groundedness).</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>60</v>
@@ -1143,7 +1143,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Versioned definition, Code review.</t>
+          <t>Để bảo đảm tính nhất quán và khả năng tái lập giữa các môi trường, toàn bộ cấu hình bảng điều khiển phải được quản lý dưới dạng mã nguồn (Dashboard-as-Code), có quy trình kiểm thử và review trước khi triển khai.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1191,7 +1191,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: User-visible symptom, Cause candidate.</t>
+          <t>Nguyên tắc phát cảnh báo SRE: Chỉ phát cảnh báo khẩn cấp (page on-call) khi có triệu chứng ảnh hưởng trực tiếp đến người dùng (breach SLO/latency); các chỉ số tài nguyên như GPU 95% chỉ dùng để chẩn đoán nguyên nhân.</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1239,7 +1239,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Condition/duration, Severity.</t>
+          <t>Cảnh báo có thể hành động được (actionable alert) bắt buộc phải cung cấp đầy đủ: Điều kiện kích hoạt, thời gian duy trì, mức độ ảnh hưởng, liên kết bằng chứng và quy trình/người chịu trách nhiệm xử lý.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1441,7 +1441,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đổi 0,1% thành tỷ lệ rồi nhân tổng phút trong window.</t>
+          <t>Tổng số phút trong cửa sổ 30 ngày: 30 ngày * 24 giờ/ngày * 60 phút/giờ = 43.200 phút. Thời gian downtime cho phép với SLO 99,9%: 43.200 * (100% - 99,9%) = 43.200 * 0,001 = 43,2 phút.</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1537,7 +1537,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Burn-rate denominator, Short window.</t>
+          <t>Quy tắc cảnh báo đa cửa sổ (multi-window multi-burn-rate) yêu cầu cả cửa sổ ngắn (5m) và cửa sổ dài (1h) đều phải vượt ngưỡng; hiện tại cửa sổ dài mới đạt 8x (&lt; 14,4x) nên không được phát trang khẩn cấp để tránh báo động giả.</t>
         </is>
       </c>
     </row>
